--- a/artfynd/A 9785-2024 artfynd.xlsx
+++ b/artfynd/A 9785-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120334586</v>
+        <v>120334579</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>77926</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422025</v>
+        <v>421958</v>
       </c>
       <c r="R2" t="n">
-        <v>6821587</v>
+        <v>6821605</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334574</v>
+        <v>120334575</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>91481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4745</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422330</v>
+        <v>422157</v>
       </c>
       <c r="R3" t="n">
-        <v>6821532</v>
+        <v>6821641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334582</v>
+        <v>120334574</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422240</v>
+        <v>422330</v>
       </c>
       <c r="R4" t="n">
-        <v>6821751</v>
+        <v>6821532</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334579</v>
+        <v>120334586</v>
       </c>
       <c r="B5" t="n">
-        <v>77926</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421958</v>
+        <v>422025</v>
       </c>
       <c r="R5" t="n">
-        <v>6821605</v>
+        <v>6821587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120334575</v>
+        <v>120334582</v>
       </c>
       <c r="B6" t="n">
-        <v>91481</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422157</v>
+        <v>422240</v>
       </c>
       <c r="R6" t="n">
-        <v>6821641</v>
+        <v>6821751</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 9785-2024 artfynd.xlsx
+++ b/artfynd/A 9785-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120334579</v>
+        <v>120334586</v>
       </c>
       <c r="B2" t="n">
-        <v>77926</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421958</v>
+        <v>422025</v>
       </c>
       <c r="R2" t="n">
-        <v>6821605</v>
+        <v>6821587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334575</v>
+        <v>120334582</v>
       </c>
       <c r="B3" t="n">
-        <v>91481</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422157</v>
+        <v>422240</v>
       </c>
       <c r="R3" t="n">
-        <v>6821641</v>
+        <v>6821751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334574</v>
+        <v>120334575</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>91481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4745</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422330</v>
+        <v>422157</v>
       </c>
       <c r="R4" t="n">
-        <v>6821532</v>
+        <v>6821641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334586</v>
+        <v>120334579</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>77926</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422025</v>
+        <v>421958</v>
       </c>
       <c r="R5" t="n">
-        <v>6821587</v>
+        <v>6821605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120334582</v>
+        <v>120334574</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422240</v>
+        <v>422330</v>
       </c>
       <c r="R6" t="n">
-        <v>6821751</v>
+        <v>6821532</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 9785-2024 artfynd.xlsx
+++ b/artfynd/A 9785-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120334586</v>
+        <v>120334582</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422025</v>
+        <v>422240</v>
       </c>
       <c r="R2" t="n">
-        <v>6821587</v>
+        <v>6821751</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334582</v>
+        <v>120334579</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>77926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422240</v>
+        <v>421958</v>
       </c>
       <c r="R3" t="n">
-        <v>6821751</v>
+        <v>6821605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334575</v>
+        <v>120334574</v>
       </c>
       <c r="B4" t="n">
-        <v>91481</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4745</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422157</v>
+        <v>422330</v>
       </c>
       <c r="R4" t="n">
-        <v>6821641</v>
+        <v>6821532</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334579</v>
+        <v>120334586</v>
       </c>
       <c r="B5" t="n">
-        <v>77926</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421958</v>
+        <v>422025</v>
       </c>
       <c r="R5" t="n">
-        <v>6821605</v>
+        <v>6821587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120334574</v>
+        <v>120334575</v>
       </c>
       <c r="B6" t="n">
-        <v>78278</v>
+        <v>91481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4745</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422330</v>
+        <v>422157</v>
       </c>
       <c r="R6" t="n">
-        <v>6821532</v>
+        <v>6821641</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 9785-2024 artfynd.xlsx
+++ b/artfynd/A 9785-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120334582</v>
+        <v>120334575</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422240</v>
+        <v>422157</v>
       </c>
       <c r="R2" t="n">
-        <v>6821751</v>
+        <v>6821641</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334579</v>
+        <v>120334582</v>
       </c>
       <c r="B3" t="n">
-        <v>77926</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421958</v>
+        <v>422240</v>
       </c>
       <c r="R3" t="n">
-        <v>6821605</v>
+        <v>6821751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334574</v>
+        <v>120334579</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>77926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422330</v>
+        <v>421958</v>
       </c>
       <c r="R4" t="n">
-        <v>6821532</v>
+        <v>6821605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334586</v>
+        <v>120334574</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422025</v>
+        <v>422330</v>
       </c>
       <c r="R5" t="n">
-        <v>6821587</v>
+        <v>6821532</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120334575</v>
+        <v>120334586</v>
       </c>
       <c r="B6" t="n">
-        <v>91481</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4745</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422157</v>
+        <v>422025</v>
       </c>
       <c r="R6" t="n">
-        <v>6821641</v>
+        <v>6821587</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 9785-2024 artfynd.xlsx
+++ b/artfynd/A 9785-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120334575</v>
+        <v>120334579</v>
       </c>
       <c r="B2" t="n">
-        <v>91481</v>
+        <v>77926</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422157</v>
+        <v>421958</v>
       </c>
       <c r="R2" t="n">
-        <v>6821641</v>
+        <v>6821605</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334582</v>
+        <v>120334575</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>91481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422240</v>
+        <v>422157</v>
       </c>
       <c r="R3" t="n">
-        <v>6821751</v>
+        <v>6821641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334579</v>
+        <v>120334586</v>
       </c>
       <c r="B4" t="n">
-        <v>77926</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421958</v>
+        <v>422025</v>
       </c>
       <c r="R4" t="n">
-        <v>6821605</v>
+        <v>6821587</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334574</v>
+        <v>120334582</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422330</v>
+        <v>422240</v>
       </c>
       <c r="R5" t="n">
-        <v>6821532</v>
+        <v>6821751</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120334586</v>
+        <v>120334574</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422025</v>
+        <v>422330</v>
       </c>
       <c r="R6" t="n">
-        <v>6821587</v>
+        <v>6821532</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 9785-2024 artfynd.xlsx
+++ b/artfynd/A 9785-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334586</v>
+        <v>120334582</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422025</v>
+        <v>422240</v>
       </c>
       <c r="R4" t="n">
-        <v>6821587</v>
+        <v>6821751</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334582</v>
+        <v>120334586</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422240</v>
+        <v>422025</v>
       </c>
       <c r="R5" t="n">
-        <v>6821751</v>
+        <v>6821587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 9785-2024 artfynd.xlsx
+++ b/artfynd/A 9785-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334575</v>
+        <v>120334582</v>
       </c>
       <c r="B3" t="n">
-        <v>91481</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422157</v>
+        <v>422240</v>
       </c>
       <c r="R3" t="n">
-        <v>6821641</v>
+        <v>6821751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334582</v>
+        <v>120334586</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422240</v>
+        <v>422025</v>
       </c>
       <c r="R4" t="n">
-        <v>6821751</v>
+        <v>6821587</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334586</v>
+        <v>120334575</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>91481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>4745</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422025</v>
+        <v>422157</v>
       </c>
       <c r="R5" t="n">
-        <v>6821587</v>
+        <v>6821641</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
